--- a/DataConstantTemperature/3MaterialsBridge.xlsx
+++ b/DataConstantTemperature/3MaterialsBridge.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ksure\Dropbox\Personal\suresh\Software\Github\ERSL-Private\METALS\DataConstantTemperature\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Personal\suresh\Software\Github\ERSL-Private\METALS\DataConstantTemperature\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC93697F-FAAD-4797-A225-0102CE188221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B79B38-7458-4BB6-8094-B6DF01230FD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3030" yWindow="2270" windowWidth="19200" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -154,40 +154,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -209,39 +181,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -525,80 +494,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.6328125" style="10" customWidth="1"/>
-    <col min="2" max="702" width="20.54296875" style="10" customWidth="1"/>
-    <col min="703" max="16384" width="9.08984375" style="10"/>
+    <col min="1" max="1" width="20.6640625" style="5" customWidth="1"/>
+    <col min="2" max="702" width="20.5546875" style="5" customWidth="1"/>
+    <col min="703" max="16384" width="9.109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>0.4</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="1">
         <v>0.2</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="2">
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="3">
         <v>0.7</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="3">
         <v>0.6</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="4">
         <v>0.8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="3">
         <v>1</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="3">
         <v>1</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="4">
         <v>1</v>
       </c>
     </row>
@@ -627,12 +596,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC80EBF-8B96-4896-8C13-AD8A976D05A3}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -646,7 +615,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -660,7 +629,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -674,7 +643,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -688,7 +657,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
